--- a/data/eu_bladder_sites_from_ctgov.xlsx
+++ b/data/eu_bladder_sites_from_ctgov.xlsx
@@ -6292,22 +6292,10 @@
           <t>NCT06020651</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>RECRUITING</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>CONTACT: Isabelle Sauret, MBS</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>CONTACT: Mariana Mirabel, MD, PhD</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
@@ -14992,7 +14980,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Injections of Botulinum Toxin a or Anticholinergic Treatment As First Line Therapy to Treat Neurogenic Overactive Bladder in Patients with Multiple Sclerosis</t>
+          <t>Injections of Botulinum Toxin A or Anticholinergic Treatment as First Line Therapy to Treat Neurogenic Overactive Bladder in Patients With Multiple Sclerosis</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">

--- a/data/eu_bladder_sites_from_ctgov.xlsx
+++ b/data/eu_bladder_sites_from_ctgov.xlsx
@@ -3183,7 +3183,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
@@ -3295,7 +3299,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
@@ -3511,7 +3519,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
@@ -3619,7 +3631,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
@@ -3679,7 +3695,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
@@ -3937,7 +3957,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
@@ -4412,7 +4436,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
@@ -4524,7 +4552,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
@@ -4703,7 +4735,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
@@ -5030,7 +5066,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
@@ -5300,7 +5340,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
@@ -5952,7 +5996,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
@@ -6124,7 +6172,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
@@ -6184,7 +6236,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
@@ -7015,7 +7071,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
@@ -7127,7 +7187,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
@@ -7494,7 +7558,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
@@ -7650,7 +7718,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>NOT_YET_RECRUITING</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
@@ -7976,7 +8048,11 @@
           <t>NCT07027020</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>RECRUITING</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>

--- a/data/eu_bladder_sites_from_ctgov.xlsx
+++ b/data/eu_bladder_sites_from_ctgov.xlsx
@@ -3250,7 +3250,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3470,7 +3470,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4387,7 +4387,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -4802,7 +4802,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -6499,7 +6499,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -7350,7 +7350,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -7999,7 +7999,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (CHU Rennes); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (CHU Rennes)</t>
+          <t>STUDY_CHAIR: Jean-Michel Reymann, PhD (Rennes University Hospital); PRINCIPAL_INVESTIGATOR: Philippe Gallien, MD (Rennes University Hospital)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
